--- a/data/synthetic/acceptance/dataset.xlsx
+++ b/data/synthetic/acceptance/dataset.xlsx
@@ -14484,7 +14484,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14662,7 +14662,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -15653,12 +15653,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>2030-01-15T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>2030-01-15T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>2030-01-15T13:30:00+03:00</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2030-01-15T13:30:00+03:00</t>
+          <t>2030-01-15T14:00:00+03:00</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
